--- a/customer+performance+additional.xlsx
+++ b/customer+performance+additional.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suraj\jup-note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00472567-01B1-455E-B088-207E2B35A9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C81FA9-D7C0-4AA8-985C-C4ABEF038777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -747,11 +747,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1063,9 +1071,9 @@
     <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -1093,13 +1101,13 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1140,13 +1148,13 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="5">
         <v>10</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="3">
         <v>98.241</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="5">
         <v>3</v>
       </c>
       <c r="J2" t="s">
@@ -1187,13 +1195,13 @@
       <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="5">
         <v>15</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <v>157.63999999999999</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>4</v>
       </c>
       <c r="J3" t="s">
@@ -1234,13 +1242,13 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
         <v>41.252000000000002</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="5">
         <v>1</v>
       </c>
       <c r="J4" t="s">
@@ -1281,13 +1289,13 @@
       <c r="F5" t="s">
         <v>32</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="5">
         <v>6</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>67.328999999999994</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
@@ -1328,13 +1336,13 @@
       <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
+      <c r="G6" s="5">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3">
         <v>52.762999999999998</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>1</v>
       </c>
       <c r="J6" t="s">
@@ -1375,13 +1383,13 @@
       <c r="F7" t="s">
         <v>32</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="5">
         <v>11</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="3">
         <v>117.012</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>3</v>
       </c>
       <c r="J7" t="s">
@@ -1422,13 +1430,13 @@
       <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="5">
         <v>9</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="3">
         <v>95.543999999999997</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>2</v>
       </c>
       <c r="J8" t="s">
@@ -1469,13 +1477,13 @@
       <c r="F9" t="s">
         <v>25</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="5">
         <v>6</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="3">
         <v>70.73</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>2</v>
       </c>
       <c r="J9" t="s">
@@ -1516,13 +1524,13 @@
       <c r="F10" t="s">
         <v>18</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="5">
         <v>12</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="3">
         <v>124.887</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="5">
         <v>3</v>
       </c>
       <c r="J10" t="s">
@@ -1563,13 +1571,13 @@
       <c r="F11" t="s">
         <v>18</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="5">
         <v>10</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="3">
         <v>108.148</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="5">
         <v>3</v>
       </c>
       <c r="J11" t="s">
@@ -1610,13 +1618,13 @@
       <c r="F12" t="s">
         <v>32</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="5">
         <v>10</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="3">
         <v>98.448999999999998</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="5">
         <v>3</v>
       </c>
       <c r="J12" t="s">
@@ -1657,13 +1665,13 @@
       <c r="F13" t="s">
         <v>32</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="5">
         <v>8</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="3">
         <v>85.43</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="5">
         <v>2</v>
       </c>
       <c r="J13" t="s">
@@ -1704,13 +1712,13 @@
       <c r="F14" t="s">
         <v>25</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="5">
         <v>10</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="3">
         <v>103.476</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="5">
         <v>3</v>
       </c>
       <c r="J14" t="s">
@@ -1751,13 +1759,13 @@
       <c r="F15" t="s">
         <v>32</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="5">
         <v>11</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="3">
         <v>111.194</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="5">
         <v>3</v>
       </c>
       <c r="J15" t="s">
@@ -1798,13 +1806,13 @@
       <c r="F16" t="s">
         <v>18</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="5">
         <v>9</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="3">
         <v>96.472999999999999</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="5">
         <v>3</v>
       </c>
       <c r="J16" t="s">
@@ -1845,13 +1853,13 @@
       <c r="F17" t="s">
         <v>32</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="5">
         <v>10</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="3">
         <v>108.902</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="5">
         <v>3</v>
       </c>
       <c r="J17" t="s">
@@ -1892,13 +1900,13 @@
       <c r="F18" t="s">
         <v>25</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="5">
         <v>13</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="3">
         <v>131.92699999999999</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="5">
         <v>4</v>
       </c>
       <c r="J18" t="s">
@@ -1939,13 +1947,13 @@
       <c r="F19" t="s">
         <v>32</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="5">
         <v>11</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="3">
         <v>118.57899999999999</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="5">
         <v>3</v>
       </c>
       <c r="J19" t="s">
@@ -1986,13 +1994,13 @@
       <c r="F20" t="s">
         <v>25</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="5">
         <v>14</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="3">
         <v>133.22900000000001</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="5">
         <v>4</v>
       </c>
       <c r="J20" t="s">
@@ -2033,13 +2041,13 @@
       <c r="F21" t="s">
         <v>32</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="5">
         <v>6</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="3">
         <v>71.789000000000001</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="5">
         <v>2</v>
       </c>
       <c r="J21" t="s">
@@ -2080,13 +2088,13 @@
       <c r="F22" t="s">
         <v>18</v>
       </c>
-      <c r="G22">
-        <v>4</v>
-      </c>
-      <c r="H22">
+      <c r="G22" s="5">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3">
         <v>54.598999999999997</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="5">
         <v>1</v>
       </c>
       <c r="J22" t="s">
@@ -2127,13 +2135,13 @@
       <c r="F23" t="s">
         <v>32</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="5">
         <v>7</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="3">
         <v>76.825999999999993</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="5">
         <v>2</v>
       </c>
       <c r="J23" t="s">
@@ -2174,13 +2182,13 @@
       <c r="F24" t="s">
         <v>32</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="5">
         <v>14</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="3">
         <v>137.697</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="5">
         <v>4</v>
       </c>
       <c r="J24" t="s">
@@ -2221,13 +2229,13 @@
       <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="5">
         <v>12</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="3">
         <v>125.76300000000001</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="5">
         <v>3</v>
       </c>
       <c r="J25" t="s">
@@ -2268,13 +2276,13 @@
       <c r="F26" t="s">
         <v>25</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="5">
         <v>12</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="3">
         <v>127.88800000000001</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="5">
         <v>3</v>
       </c>
       <c r="J26" t="s">
@@ -2315,13 +2323,13 @@
       <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="5">
         <v>5</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="3">
         <v>58.264000000000003</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="5">
         <v>1</v>
       </c>
       <c r="J27" t="s">
@@ -2362,13 +2370,13 @@
       <c r="F28" t="s">
         <v>18</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="5">
         <v>14</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="3">
         <v>137.17099999999999</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="5">
         <v>4</v>
       </c>
       <c r="J28" t="s">
@@ -2409,13 +2417,13 @@
       <c r="F29" t="s">
         <v>18</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="5">
         <v>10</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="3">
         <v>102.946</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="5">
         <v>3</v>
       </c>
       <c r="J29" t="s">
@@ -2456,13 +2464,13 @@
       <c r="F30" t="s">
         <v>25</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="5">
         <v>12</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="3">
         <v>127.16500000000001</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="5">
         <v>3</v>
       </c>
       <c r="J30" t="s">
@@ -2503,13 +2511,13 @@
       <c r="F31" t="s">
         <v>25</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="5">
         <v>13</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="3">
         <v>132.035</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="5">
         <v>4</v>
       </c>
       <c r="J31" t="s">
@@ -2550,13 +2558,13 @@
       <c r="F32" t="s">
         <v>32</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="5">
         <v>12</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="3">
         <v>121.402</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="5">
         <v>3</v>
       </c>
       <c r="J32" t="s">
@@ -2597,13 +2605,13 @@
       <c r="F33" t="s">
         <v>32</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="5">
         <v>12</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="3">
         <v>120.92100000000001</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="5">
         <v>3</v>
       </c>
       <c r="J33" t="s">
@@ -2644,13 +2652,13 @@
       <c r="F34" t="s">
         <v>25</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="5">
         <v>7</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="3">
         <v>76.114000000000004</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="5">
         <v>2</v>
       </c>
       <c r="J34" t="s">
@@ -2691,13 +2699,13 @@
       <c r="F35" t="s">
         <v>18</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="5">
         <v>12</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="3">
         <v>130.27699999999999</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="5">
         <v>3</v>
       </c>
       <c r="J35" t="s">
@@ -2738,13 +2746,13 @@
       <c r="F36" t="s">
         <v>25</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="5">
         <v>7</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="3">
         <v>75.567999999999998</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="5">
         <v>2</v>
       </c>
       <c r="J36" t="s">
@@ -2785,13 +2793,13 @@
       <c r="F37" t="s">
         <v>25</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="5">
         <v>5</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="3">
         <v>65.356999999999999</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="5">
         <v>1</v>
       </c>
       <c r="J37" t="s">
@@ -2832,13 +2840,13 @@
       <c r="F38" t="s">
         <v>18</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="5">
         <v>8</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="3">
         <v>85.129000000000005</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="5">
         <v>2</v>
       </c>
       <c r="J38" t="s">
@@ -2879,13 +2887,13 @@
       <c r="F39" t="s">
         <v>25</v>
       </c>
-      <c r="G39">
-        <v>2</v>
-      </c>
-      <c r="H39">
+      <c r="G39" s="5">
+        <v>2</v>
+      </c>
+      <c r="H39" s="3">
         <v>46.456000000000003</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="5">
         <v>1</v>
       </c>
       <c r="J39" t="s">
@@ -2926,13 +2934,13 @@
       <c r="F40" t="s">
         <v>25</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="5">
         <v>14</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="3">
         <v>133.54</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="5">
         <v>4</v>
       </c>
       <c r="J40" t="s">
@@ -2973,13 +2981,13 @@
       <c r="F41" t="s">
         <v>18</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="5">
         <v>7</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="3">
         <v>78.414000000000001</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="5">
         <v>2</v>
       </c>
       <c r="J41" t="s">
@@ -3020,13 +3028,13 @@
       <c r="F42" t="s">
         <v>18</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="5">
         <v>12</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="3">
         <v>125.185</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="5">
         <v>3</v>
       </c>
       <c r="J42" t="s">
@@ -3067,13 +3075,13 @@
       <c r="F43" t="s">
         <v>18</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="5">
         <v>11</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="3">
         <v>120.31100000000001</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="5">
         <v>3</v>
       </c>
       <c r="J43" t="s">
@@ -3114,13 +3122,13 @@
       <c r="F44" t="s">
         <v>32</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="5">
         <v>12</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="3">
         <v>130.56200000000001</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="5">
         <v>3</v>
       </c>
       <c r="J44" t="s">
@@ -3161,13 +3169,13 @@
       <c r="F45" t="s">
         <v>32</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="5">
         <v>8</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="3">
         <v>88.418999999999997</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="5">
         <v>2</v>
       </c>
       <c r="J45" t="s">
@@ -3205,13 +3213,13 @@
       <c r="F46" t="s">
         <v>25</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="5">
         <v>8</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="3">
         <v>86.903999999999996</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="5">
         <v>2</v>
       </c>
       <c r="J46" t="s">
@@ -3252,13 +3260,13 @@
       <c r="F47" t="s">
         <v>25</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="5">
         <v>15</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="3">
         <v>152.291</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="5">
         <v>4</v>
       </c>
       <c r="J47" t="s">
@@ -3299,13 +3307,13 @@
       <c r="F48" t="s">
         <v>18</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="5">
         <v>11</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="3">
         <v>110.97</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="5">
         <v>3</v>
       </c>
       <c r="J48" t="s">
@@ -3346,13 +3354,13 @@
       <c r="F49" t="s">
         <v>25</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="5">
         <v>8</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="3">
         <v>85.194000000000003</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="5">
         <v>2</v>
       </c>
       <c r="J49" t="s">
@@ -3393,13 +3401,13 @@
       <c r="F50" t="s">
         <v>25</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="5">
         <v>12</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="3">
         <v>129.524</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="5">
         <v>3</v>
       </c>
       <c r="J50" t="s">
@@ -3437,13 +3445,13 @@
       <c r="F51" t="s">
         <v>32</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="5">
         <v>7</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="3">
         <v>84.460999999999999</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="5">
         <v>2</v>
       </c>
       <c r="J51" t="s">
@@ -3484,13 +3492,13 @@
       <c r="F52" t="s">
         <v>32</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="5">
         <v>10</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="3">
         <v>97.781999999999996</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="5">
         <v>3</v>
       </c>
       <c r="J52" t="s">
@@ -3531,13 +3539,13 @@
       <c r="F53" t="s">
         <v>25</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="5">
         <v>6</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="3">
         <v>68.116</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="5">
         <v>1</v>
       </c>
       <c r="J53" t="s">
@@ -3578,13 +3586,13 @@
       <c r="F54" t="s">
         <v>18</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="5">
         <v>10</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="3">
         <v>105.28700000000001</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="5">
         <v>3</v>
       </c>
       <c r="J54" t="s">
@@ -3625,13 +3633,13 @@
       <c r="F55" t="s">
         <v>18</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="5">
         <v>7</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="3">
         <v>73.408000000000001</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="5">
         <v>2</v>
       </c>
       <c r="J55" t="s">
@@ -3672,13 +3680,13 @@
       <c r="F56" t="s">
         <v>25</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="5">
         <v>5</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="3">
         <v>59.387999999999998</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="5">
         <v>1</v>
       </c>
       <c r="J56" t="s">
@@ -3716,13 +3724,13 @@
       <c r="F57" t="s">
         <v>18</v>
       </c>
-      <c r="G57">
-        <v>3</v>
-      </c>
-      <c r="H57">
+      <c r="G57" s="5">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
         <v>47.877000000000002</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="5">
         <v>1</v>
       </c>
       <c r="J57" t="s">
@@ -3763,13 +3771,13 @@
       <c r="F58" t="s">
         <v>18</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="5">
         <v>9</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="3">
         <v>93.78</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="5">
         <v>2</v>
       </c>
       <c r="J58" t="s">
@@ -3810,13 +3818,13 @@
       <c r="F59" t="s">
         <v>25</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="5">
         <v>7</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="3">
         <v>81.111000000000004</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="5">
         <v>2</v>
       </c>
       <c r="J59" t="s">
@@ -3854,13 +3862,13 @@
       <c r="F60" t="s">
         <v>32</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="5">
         <v>8</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="3">
         <v>86.206999999999994</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="5">
         <v>2</v>
       </c>
       <c r="J60" t="s">
@@ -3901,13 +3909,13 @@
       <c r="F61" t="s">
         <v>32</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="5">
         <v>6</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="3">
         <v>68.405000000000001</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="5">
         <v>1</v>
       </c>
       <c r="J61" t="s">
@@ -3948,13 +3956,13 @@
       <c r="F62" t="s">
         <v>25</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="5">
         <v>16</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="3">
         <v>193.04599999999999</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="5">
         <v>5</v>
       </c>
       <c r="J62" t="s">
@@ -3995,13 +4003,13 @@
       <c r="F63" t="s">
         <v>32</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="5">
         <v>7</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="3">
         <v>78.158000000000001</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="5">
         <v>2</v>
       </c>
       <c r="J63" t="s">
@@ -4042,13 +4050,13 @@
       <c r="F64" t="s">
         <v>25</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="5">
         <v>10</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="3">
         <v>96.552999999999997</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="5">
         <v>3</v>
       </c>
       <c r="J64" t="s">
@@ -4086,13 +4094,13 @@
       <c r="F65" t="s">
         <v>25</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="5">
         <v>10</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="3">
         <v>107.919</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="5">
         <v>3</v>
       </c>
       <c r="J65" t="s">
@@ -4133,13 +4141,13 @@
       <c r="F66" t="s">
         <v>25</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="5">
         <v>9</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="3">
         <v>94.468999999999994</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="5">
         <v>2</v>
       </c>
       <c r="J66" t="s">
@@ -4180,13 +4188,13 @@
       <c r="F67" t="s">
         <v>18</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="5">
         <v>11</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="3">
         <v>112.72199999999999</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="5">
         <v>3</v>
       </c>
       <c r="J67" t="s">
@@ -4224,13 +4232,13 @@
       <c r="F68" t="s">
         <v>25</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="5">
         <v>12</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="3">
         <v>128.255</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="5">
         <v>3</v>
       </c>
       <c r="J68" t="s">
@@ -4271,13 +4279,13 @@
       <c r="F69" t="s">
         <v>18</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="5">
         <v>10</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="3">
         <v>101.08799999999999</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="5">
         <v>3</v>
       </c>
       <c r="J69" t="s">
@@ -4318,13 +4326,13 @@
       <c r="F70" t="s">
         <v>32</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="5">
         <v>9</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="3">
         <v>96.441999999999993</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="5">
         <v>2</v>
       </c>
       <c r="J70" t="s">
@@ -4362,13 +4370,13 @@
       <c r="F71" t="s">
         <v>18</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="5">
         <v>8</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="3">
         <v>85.831999999999994</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="5">
         <v>2</v>
       </c>
       <c r="J71" t="s">
@@ -4409,13 +4417,13 @@
       <c r="F72" t="s">
         <v>18</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="5">
         <v>11</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="3">
         <v>117.39400000000001</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="5">
         <v>3</v>
       </c>
       <c r="J72" t="s">
@@ -4456,13 +4464,13 @@
       <c r="F73" t="s">
         <v>32</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="5">
         <v>5</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="3">
         <v>61.191000000000003</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="5">
         <v>1</v>
       </c>
       <c r="J73" t="s">
@@ -4503,13 +4511,13 @@
       <c r="F74" t="s">
         <v>25</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="5">
         <v>9</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="3">
         <v>90.343999999999994</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="5">
         <v>2</v>
       </c>
       <c r="J74" t="s">
@@ -4550,13 +4558,13 @@
       <c r="F75" t="s">
         <v>25</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="5">
         <v>5</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="3">
         <v>65.224000000000004</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="5">
         <v>1</v>
       </c>
       <c r="J75" t="s">
@@ -4594,13 +4602,13 @@
       <c r="F76" t="s">
         <v>18</v>
       </c>
-      <c r="G76">
-        <v>4</v>
-      </c>
-      <c r="H76">
+      <c r="G76" s="5">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3">
         <v>57.984000000000002</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="5">
         <v>1</v>
       </c>
       <c r="J76" t="s">
@@ -4641,13 +4649,13 @@
       <c r="F77" t="s">
         <v>32</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="5">
         <v>14</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="3">
         <v>134.54</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="5">
         <v>4</v>
       </c>
       <c r="J77" t="s">
@@ -4688,13 +4696,13 @@
       <c r="F78" t="s">
         <v>32</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="5">
         <v>5</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="3">
         <v>63.082000000000001</v>
       </c>
-      <c r="I78" t="s">
+      <c r="I78" s="5" t="s">
         <v>180</v>
       </c>
       <c r="J78" t="s">
@@ -4735,13 +4743,13 @@
       <c r="F79" t="s">
         <v>32</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="5">
         <v>7</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="3">
         <v>80.816000000000003</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="5">
         <v>2</v>
       </c>
       <c r="J79" t="s">
@@ -4782,13 +4790,13 @@
       <c r="F80" t="s">
         <v>25</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="5">
         <v>11</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="3">
         <v>13423411.958000001</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="5">
         <v>3</v>
       </c>
       <c r="J80" t="s">
@@ -4829,13 +4837,13 @@
       <c r="F81" t="s">
         <v>18</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="5">
         <v>9</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="3">
         <v>91.536000000000001</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="5">
         <v>2</v>
       </c>
       <c r="J81" t="s">
@@ -4876,13 +4884,13 @@
       <c r="F82" t="s">
         <v>18</v>
       </c>
-      <c r="G82">
-        <v>4</v>
-      </c>
-      <c r="H82">
+      <c r="G82" s="5">
+        <v>4</v>
+      </c>
+      <c r="H82" s="3">
         <v>54.598999999999997</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="5">
         <v>1</v>
       </c>
       <c r="J82" t="s">
@@ -4923,13 +4931,13 @@
       <c r="F83" t="s">
         <v>25</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="5">
         <v>11</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="3">
         <v>75.757000000000005</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="5">
         <v>2</v>
       </c>
       <c r="J83" t="s">
@@ -4970,13 +4978,13 @@
       <c r="F84" t="s">
         <v>32</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="5">
         <v>9</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="3">
         <v>78.433000000000007</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="5">
         <v>4</v>
       </c>
       <c r="J84" t="s">
@@ -5017,13 +5025,13 @@
       <c r="F85" t="s">
         <v>18</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="5">
         <v>7</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="3">
         <v>82.793999999999997</v>
       </c>
-      <c r="I85">
+      <c r="I85" s="5">
         <v>3</v>
       </c>
       <c r="J85" t="s">
@@ -5064,13 +5072,13 @@
       <c r="F86" t="s">
         <v>25</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="5">
         <v>15</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="3">
         <v>88.49</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="5">
         <v>2</v>
       </c>
       <c r="J86" t="s">
@@ -5111,13 +5119,13 @@
       <c r="F87" t="s">
         <v>32</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="5">
         <v>13</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="3">
         <v>108.749</v>
       </c>
-      <c r="I87">
+      <c r="I87" s="5">
         <v>3</v>
       </c>
       <c r="J87" t="s">
@@ -5158,13 +5166,13 @@
       <c r="F88" t="s">
         <v>25</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="5">
         <v>14</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="3">
         <v>102.18600000000001</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="5">
         <v>4</v>
       </c>
       <c r="J88" t="s">
@@ -5205,13 +5213,13 @@
       <c r="F89" t="s">
         <v>25</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="5">
         <v>10</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="3">
         <v>99.442999999999998</v>
       </c>
-      <c r="I89">
+      <c r="I89" s="5">
         <v>1</v>
       </c>
       <c r="J89" t="s">
@@ -5252,13 +5260,13 @@
       <c r="F90" t="s">
         <v>25</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="5">
         <v>10</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="3">
         <v>103.001</v>
       </c>
-      <c r="I90">
+      <c r="I90" s="5">
         <v>3</v>
       </c>
       <c r="J90" t="s">
@@ -5299,13 +5307,13 @@
       <c r="F91" t="s">
         <v>32</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="5">
         <v>13</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="3">
         <v>112.842</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="5">
         <v>3</v>
       </c>
       <c r="J91" t="s">
@@ -5346,13 +5354,13 @@
       <c r="F92" t="s">
         <v>18</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="5">
         <v>8</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="3">
         <v>68.805999999999997</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="5">
         <v>3</v>
       </c>
       <c r="J92" t="s">
@@ -5393,13 +5401,13 @@
       <c r="F93" t="s">
         <v>32</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="5">
         <v>13</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="3">
         <v>108.73699999999999</v>
       </c>
-      <c r="I93">
+      <c r="I93" s="5">
         <v>3</v>
       </c>
       <c r="J93" t="s">
@@ -5440,13 +5448,13 @@
       <c r="F94" t="s">
         <v>32</v>
       </c>
-      <c r="G94">
+      <c r="G94" s="5">
         <v>9</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="3">
         <v>99.826999999999998</v>
       </c>
-      <c r="I94">
+      <c r="I94" s="5">
         <v>4</v>
       </c>
       <c r="J94" t="s">
@@ -5487,13 +5495,13 @@
       <c r="F95" t="s">
         <v>32</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="5">
         <v>12</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="3">
         <v>70.519000000000005</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="5">
         <v>0</v>
       </c>
       <c r="J95" t="s">
@@ -5534,13 +5542,13 @@
       <c r="F96" t="s">
         <v>32</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="5">
         <v>10</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="3">
         <v>75.875</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="5">
         <v>4</v>
       </c>
       <c r="J96" t="s">
@@ -5581,13 +5589,13 @@
       <c r="F97" t="s">
         <v>32</v>
       </c>
-      <c r="G97">
+      <c r="G97" s="5">
         <v>8</v>
       </c>
-      <c r="H97">
+      <c r="H97" s="3">
         <v>64.054000000000002</v>
       </c>
-      <c r="I97">
+      <c r="I97" s="5">
         <v>4</v>
       </c>
       <c r="J97" t="s">
@@ -5628,13 +5636,13 @@
       <c r="F98" t="s">
         <v>18</v>
       </c>
-      <c r="G98">
+      <c r="G98" s="5">
         <v>12</v>
       </c>
-      <c r="H98">
+      <c r="H98" s="3">
         <v>123.003</v>
       </c>
-      <c r="I98">
+      <c r="I98" s="5">
         <v>4</v>
       </c>
       <c r="J98" t="s">
@@ -5675,13 +5683,13 @@
       <c r="F99" t="s">
         <v>25</v>
       </c>
-      <c r="G99">
+      <c r="G99" s="5">
         <v>13</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="3">
         <v>106.526</v>
       </c>
-      <c r="I99">
+      <c r="I99" s="5">
         <v>4</v>
       </c>
       <c r="J99" t="s">
@@ -5722,13 +5730,13 @@
       <c r="F100" t="s">
         <v>25</v>
       </c>
-      <c r="G100">
-        <v>3</v>
-      </c>
-      <c r="H100">
+      <c r="G100" s="5">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3">
         <v>162.53299999999999</v>
       </c>
-      <c r="I100">
+      <c r="I100" s="5">
         <v>1</v>
       </c>
       <c r="J100" t="s">
@@ -5769,13 +5777,13 @@
       <c r="F101" t="s">
         <v>32</v>
       </c>
-      <c r="G101">
+      <c r="G101" s="5">
         <v>5</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="3">
         <v>145.404</v>
       </c>
-      <c r="I101">
+      <c r="I101" s="5">
         <v>2</v>
       </c>
       <c r="J101" t="s">
@@ -5816,13 +5824,13 @@
       <c r="F102" t="s">
         <v>32</v>
       </c>
-      <c r="G102">
+      <c r="G102" s="5">
         <v>14</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="3">
         <v>36.975000000000001</v>
       </c>
-      <c r="I102">
+      <c r="I102" s="5">
         <v>2</v>
       </c>
       <c r="J102" t="s">
